--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1046,6 +1046,43 @@
       </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Felicia (Andriani S.p.A.)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Organic buckwheat/whole-grain gluten-free pasta</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Parent company Andriani S.p.A. is a certified B Corp</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Felicia is the consumer brand of Andriani S.p.A. (already a verified B Corp in this shortlist's Grains sheet) -- vertically integrated supply chain of 500+ farmers across ~8,500 hectares, largest dried-legume supplier in Italy. Note: may overlap with the existing Andriani row -- confirm before adding both.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://felicia.us/about-felicia/</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1057,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1402,72 +1439,6 @@
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Auntie Rana's</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Hummus</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>5% of profits donated to wildlife conservation</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Founder-driven, named percentage commitment (5% of profits) to protect endangered species (elephants, macaques, Irrawaddy dolphins) tied directly to her childhood in Bangladesh.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>https://auntieranas.com/</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Felicia (Andriani S.p.A.)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Organic legume &amp; grain pasta (lentil, buckwheat, spirulina)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Parent company Andriani S.p.A. is a certified B Corp</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Felicia is the consumer brand of Andriani S.p.A. (already a verified B Corp in this shortlist's Grains sheet) -- vertically integrated supply chain of 500+ farmers across ~8,500 hectares, largest dried-legume supplier in Italy. Note: may overlap with the existing Andriani row -- confirm before adding both.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>https://felicia.us/about-felicia/</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1956,7 +1927,11 @@
           <t>https://brassrootsfood.com/</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1989,7 +1964,11 @@
           <t>https://cactus-foods.com/</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2022,7 +2001,11 @@
           <t>https://chocxo.com/pages/about-chocxo</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2055,7 +2038,11 @@
           <t>https://www.dirtbagbar.com/</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2088,7 +2075,11 @@
           <t>https://www.edggies.com/pages/about</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2121,7 +2112,11 @@
           <t>https://evohemp.com/</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>N (bar line discontinued — see note)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2154,7 +2149,11 @@
           <t>https://figafoods.com/pages/about-us</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2187,7 +2186,11 @@
           <t>https://figureatefoods.com/</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Y (imported under Olive Oils &amp; Condiments as persimmon vinegar)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2220,7 +2223,11 @@
           <t>https://bakeaway.com/pages/about-us</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2253,7 +2260,11 @@
           <t>https://www.defisnacks.com/</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2775,7 +2786,11 @@
           <t>https://allthebitter.com/</t>
         </is>
       </c>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2788,7 +2803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2868,7 +2883,48 @@
           <t>https://brightland.co/pages/about-brightland-olive-oil</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>N (duplicate — already live as Brightland Alive EVOO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Auntie Rana's</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Smoked Chili Oil (condiment)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>5% of profits donated to wildlife conservation</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Founder-driven, named percentage commitment (5% of profits) to protect endangered species via partnerships with Wildlife SOS (India) and Wildlife Alliance (Cambodia), tied to founder's childhood in Bangladesh. Corrected from initial research: brand is a Southeast Asian condiments line (chili oil, mayo, achaar, jam), not a hummus/legumes product.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://auntieranas.com/products/smoked-chili-oil</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -1451,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2266,6 +2266,171 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Harken Sweets</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Plant-based, no-sugar-added candy bars</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Fair Trade certified</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Plant-based reimagining of classic candy bars (Snickers/Milky Way-style) with Fair Trade certified cocoa, 75% less sugar, 13g prebiotic fiber per bar.</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>https://harkensweets.com/</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>iMind Brain Food</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Brain-health food bars</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Certified Organic (95%+ organic material)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Founded by a board-certified neurosurgeon; bars blend organic whole-food ingredients and functional botanicals. Certified organic status verified via retail sustainability-feature badge, not just brand claim.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imindbrainfood.com/</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Joey Nordic Seed Crisps</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Canada (Prince Edward County)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Seed crisps/crackers</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Certified organic, gluten-free</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Certified organic, gluten-free crisps made from 7 super seeds including upcycled watermelon seeds -- among the first snack brands to use upcycled watermelon seed as a protein source.</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>https://joeynordicseedcrisps.com/</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>kencko</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>USA / Portugal</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Organic instant smoothies, snacks</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Certified B Corp (92.0 score)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Flash-frozen, slow-dried organic fruit and vegetable smoothie powders; Certified B Corporation with a B Impact score of 92.0, independently verified by B Lab. 100% organic, no added sugar.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcorporation.net/en-us/find-a-b-corp/company/kencko/</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Kittylamb</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>USA (Scarborough, ME)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Organic baking mixes</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>MOFGA certified organic</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Certified organic (MOFGA -- Maine Organic Farmers and Gardeners Association, an independent state-level certifier) baking mixes using fair-trade ingredients where available.</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>https://kittylamb.com/</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2277,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2792,6 +2957,39 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Good Twin</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>USA (Santa Maria, CA) / Italy-produced</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Non-alcoholic sparkling wine (Glera grape)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Certified organic (Bios Srl, Italian organic certifier)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Made with real Glera grapes (the Prosecco variety), 4 ingredients, certified organic and vegan by Bios Srl -- an independent EU organic certification body, not a self-declared claim.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://drinkgoodtwin.com/</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2803,7 +3001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2926,6 +3124,39 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Harry's Famous Sauce</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Pasta sauces</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Non-GMO Project Verified + Upcycled Certified (select SKUs)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Founded by Harry Hamlin and Chef Renee Guilbault as debut line from The Open Food Company. Lemon Pepper Dill and Marinara No. 7 are Non-GMO Project certified; Lemon Pepper Dill is additionally Upcycled Certified via a Matriark Foods collaboration -- both independently audited certifications, not self-declared.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://harrysfamous.com/pages/about</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -1451,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2297,7 +2297,11 @@
           <t>https://harkensweets.com/</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2330,7 +2334,11 @@
           <t>https://www.imindbrainfood.com/</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>N (out of stock everywhere -- official site + 3 Amazon ASINs unavailable)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2363,7 +2371,11 @@
           <t>https://joeynordicseedcrisps.com/</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2396,7 +2408,11 @@
           <t>https://www.bcorporation.net/en-us/find-a-b-corp/company/kencko/</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2429,7 +2445,48 @@
           <t>https://kittylamb.com/</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>MALK Organics</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Shelf-stable oat/almond milk</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>3-ingredient shelf-stable oat milk (filtered water, organic oats, Himalayan pink salt) -- USDA Organic certified, no gums/oils/fillers. Shelf-stable format distinguishes it from perishable refrigerated dairy alternatives.</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>https://malkorganics.com/products/oat-milk</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2442,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2988,7 +3045,48 @@
           <t>https://drinkgoodtwin.com/</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Kahawa 1893 Coffee</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>USA / Kenya, Rwanda, Congo sourced</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Coffee (whole bean/ground)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Direct trade, women farmer-owned model</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Sources directly from women farmers in Kenya, Rwanda, and Congo, paying more than double the Fair Trade minimum price. Founder Margaret Nyamumbo pledges 25% of revenue to loans empowering women farmers, and the company matches customer tips to farmers dollar-for-dollar. First Black woman-owned coffee brand sold in Trader Joe's.</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://kahawa1893.com/pages/fairtrade</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3155,7 +3253,11 @@
           <t>https://harrysfamous.com/pages/about</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snacks &amp; Pantry" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Low &amp; No Alcohol" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Olive Oils &amp; Condiments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seafood" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1082,6 +1083,39 @@
           <t>Y</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Pastabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Organic pasta for kids</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic, Kosher, Certified Vegan, Non-GMO</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Four independent certifications on a pasta product -- comfortably clears the bar.</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://pastabilitiesfood.com/</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1451,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2488,6 +2522,171 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Mary's Gone Crackers</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Organic gluten-free crackers (brown rice, quinoa, flax, sesame)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic, WFCF Organic certified, Non-GMO</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Certified organic by two separate bodies (USDA + WFCF) plus Non-GMO -- strong certification stack.</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/Marys-Gone-Crackers-Original-Ounce/dp/B07HPQJQNL</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Michele's Granola</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Granola and muesli</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Non-GMO Project Verified, SQF certified, NSF P543 Vegan certified (first-ever recipient), 1% of sales to food-focused nonprofits</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Three independently administered certifications plus a quantified give-back (1% of sales, food-focused) -- clears both the cert bar and the give-back specificity bar.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.michelesgranola.com/</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>milkadamia</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Australia-sourced / USA brand</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Shelf-stable organic macadamia milk</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic certified</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic certified and shelf-stable, so it fits Snacks &amp; Pantry the same way MALK's oat milk does (not a perishable dairy substitute).</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.milkadamia.com/products/milkadamia-organic-artisan-macadamia-milk-32oz-pack-of-6</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Olyra Foods</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Greek-heritage recipe / USA</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Organic breakfast biscuits made with ancient grains</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic certification on a shelf-stable breakfast product.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>https://olyrafoods.com/</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Partake Foods</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Allergy-friendly cookies and baking mixes</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Certified B Corporation (87.1 B Impact Score, B Lab-verified), top-9-allergen-free certified, Certified Gluten-Free, Non-GMO Project Verified, Certified Vegan</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>B Corp status is independently audited by B Lab (not self-declared), plus a quantified give-back: 1% of revenue to fight food insecurity in the US.</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.partakefoods.com/</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2499,7 +2698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3088,6 +3287,39 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Matchpoint</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Japan-sourced / USA brand</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Matcha green tea powder</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>JAS Certified Organic, USDA Organic, direct trade with family-owned tencha farms</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>JAS (Japan's official organic standard) and USDA Organic are both independently administered; direct-trade sourcing from named family farms adds a fair-trade-style signal. Fits Low &amp; No Alcohol the same way yerba mate already does.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.matchpointmatcha.com/about</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3099,7 +3331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3259,6 +3491,198 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Marianne's (Marianne's Harvest)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>USA (Northern California)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Regenerative Organic Certified avocado oil</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Regenerative Organic Certified (ROC), USDA Organic, Seed Oil Free Certified</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>First refined ROC avocado oil on shelves -- ROC and USDA Organic are both independently administered, audited certifications, not self-declared claims.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://mariannesharvest.com/product/regenerative-organic-certified-avocado-oil/</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Nan's Original Recipes</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Organic, seed-oil-free salad dressings/marinades</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Certified Kosher, USDA Organic, Non-GMO Project Verified, Certified Vegan</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Four independent certifications stack on one condiment line -- clears the bar well past a single-cert minimum.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://nansfoods.com/</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Noshi (Noshi For Kids)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>USA (New York)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Organic ketchup, ranch dressing, chick'n dip for kids</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>USDA Organic, Kosher certified, Non-GMO</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Certified-organic and certified-kosher condiments aimed at kids -- independently verifiable, not just a marketing claim.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/Noshi-Sketchup-Organic-Ketchup-Decorate/dp/B0C5KKPDKM</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Brand / Producer</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Country / Region</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Product Type</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Signal(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Why It Fits</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Select? (Y/N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nice Cans</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Canada (brand) / Portugal (packed by Jose Gourmet)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Tinned sardines and seafood conservas</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Marine Stewardship Council (MSC) certified, organic ingredients where possible</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>MSC certification is independently administered and audited -- the seafood-category equivalent of Fair Trade/B Corp. Direct partnership with named small fisheries and canneries adds a fair-trade-style revenue-sharing signal.</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://justnicecans.com/</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Four independent certifications on a pasta product -- comfortably clears the bar.</t>
+          <t>Corrected after live verification: retail packaging says 'All-Natural,' not USDA Organic. Kosher Certified is the verified independent certification; imported on that single-certification basis (same bar as MSC/B Corp elsewhere on this list).</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1115,7 +1115,11 @@
           <t>https://pastabilitiesfood.com/</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2553,7 +2557,11 @@
           <t>https://www.amazon.com/Marys-Gone-Crackers-Original-Ounce/dp/B07HPQJQNL</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2586,7 +2594,11 @@
           <t>https://www.michelesgranola.com/</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2619,7 +2631,11 @@
           <t>https://www.milkadamia.com/products/milkadamia-organic-artisan-macadamia-milk-32oz-pack-of-6</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2652,7 +2668,11 @@
           <t>https://olyrafoods.com/</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2685,7 +2705,11 @@
           <t>https://www.partakefoods.com/</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3318,7 +3342,11 @@
           <t>https://www.matchpointmatcha.com/about</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3522,7 +3550,11 @@
           <t>https://mariannesharvest.com/product/regenerative-organic-certified-avocado-oil/</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -3555,7 +3587,11 @@
           <t>https://nansfoods.com/</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -3588,7 +3624,11 @@
           <t>https://www.amazon.com/Noshi-Sketchup-Organic-Ketchup-Decorate/dp/B0C5KKPDKM</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>N (certified-organic condiment line discontinued -- current live product is an uncertified 'frosting' line)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3681,7 +3721,11 @@
           <t>https://justnicecans.com/</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -1489,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2711,6 +2711,204 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SEEDLY</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Organic dark chocolate seed bark</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic, Fair Trade ingredients, Kosher Certified</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Three independent certifications (organic, fair trade, kosher) stack on one product -- comfortably clears the certification bar.</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eatseedly.com/</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Solely</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Organic 1-ingredient fruit jerky</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic (certified by Organic Certifiers), Non-GMO, Kosher</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic certification verified with a named certifying body (Organic Certifiers), plus Non-GMO and Kosher.</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>https://solely.com/products/organic-mango-fruit-jerky</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Stellar Eats</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Canada (Toronto)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Almond-flour baking mixes</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Kosher Certified, Certified Gluten-Free, Non-GMO</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Kosher Certified is an independently administered certification; qualifies on that basis alone, same bar used for other single-certification approvals on this list.</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>https://stellareats.com/en-us</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sweet Deliverance</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>USA (Kingston, NY)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Organic granola</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Certified Organic</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>All four granola flavors are certified organic, made with pure olive oil, gluten-free -- a Good Food Award winner.</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>https://sweetdeliveranceny.com/</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Sweeter Collective</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Organic long-lasting hard candy</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic hard candy made with real, organic ingredients -- an independently administered certification on a candy category where most competitors carry none.</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sweetercollective.com/</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Tazzy Candy</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Kosher lollipops and hard candy</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Kosher Certified (AKC), Gives Back -- 1% of net revenue to MBCure</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Kosher Certified by a named certifying body (AKC) qualifies on its own; the give-back is quantified though the cause (breast cancer research) isn't food/ag-specific.</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>https://tazzy.co/</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2722,7 +2920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3348,6 +3546,105 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Rare Breed Coffee (formerly A&amp;E Coffee &amp; Tea)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>USA (Nashua, NH)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Organic roasted coffee</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic (first certified organic coffee roaster in New Hampshire)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic certification on the roasting facility itself, not just the beans -- fits Low &amp; No Alcohol the same way other coffee and tea brands already do on this list.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://rarebreedcoffee.com/</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>tealish</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Canada (Toronto)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Organic loose-leaf and functional teas</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic certified tea from an independent, family-owned company -- fits Low &amp; No Alcohol per the existing yerba mate/coffee precedent.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://tealish.com/en-us/collections/organic-tea</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Three Spirit</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>UK / USA distribution</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Non-alcoholic botanical spirit</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Certified B Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>B Corp status is independently audited by B Lab, not self-declared -- qualifies on that certification alone.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://us.threespiritdrinks.com/</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3359,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3629,6 +3926,72 @@
           <t>N (certified-organic condiment line discontinued -- current live product is an uncertified 'frosting' line)</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Racha Organics</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Thailand (estate-grown) / USA brand</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Organic sriracha hot sauce</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Made with USDA-certified organic Racha chili peppers grown exclusively on the brand's own certified organic farm in northern Thailand -- an independently administered certification, not a self-declared claim.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://racha-organics.com/products/red-mild-sriracha</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Taim Olive</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Lebanon (Taim Valley) / USA brand</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Single-estate extra virgin olive oil</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Gives Back -- 1% of profits to SEAL (501(c)(3) supporting Lebanese farmers and land stewards)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Names a specific nonprofit and cause tied directly to the farmers who grow the olives -- a food/ag-relevant give-back with a real 501(c)(3), not a vague 'gives back' claim.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://taimolive.com/</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -2742,7 +2742,11 @@
           <t>https://www.eatseedly.com/</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2775,7 +2779,11 @@
           <t>https://solely.com/products/organic-mango-fruit-jerky</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2808,7 +2816,11 @@
           <t>https://stellareats.com/en-us</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2833,7 +2845,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>All four granola flavors are certified organic, made with pure olive oil, gluten-free -- a Good Food Award winner.</t>
+          <t>On live verification, brand's own site says only "we use organic ingredients wherever we can" -- no certifying body named. Good Food Award is a recognition, not an independent certification.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2841,7 +2853,11 @@
           <t>https://sweetdeliveranceny.com/</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>N (correction: brand only self-describes ingredients as organic, no certifying body named; 2024 Good Food Award is recognition, not certification)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2874,7 +2890,11 @@
           <t>https://www.sweetercollective.com/</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -2899,7 +2919,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Kosher Certified by a named certifying body (AKC) qualifies on its own; the give-back is quantified though the cause (breast cancer research) isn't food/ag-specific.</t>
+          <t>Official site unreachable; third-party retailers (Misfits Market, Snackmagic) list out of stock; no live Tazzy Candy listings found on Amazon. Discontinued/unavailable.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2907,7 +2927,11 @@
           <t>https://tazzy.co/</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>N (discontinued -- unavailable everywhere checked)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3577,7 +3601,11 @@
           <t>https://rarebreedcoffee.com/</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3602,7 +3630,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>USDA Organic certified tea from an independent, family-owned company -- fits Low &amp; No Alcohol per the existing yerba mate/coffee precedent.</t>
+          <t>On live verification, brand's own product page and packaging photo, plus every third-party retailer listing checked, repeat "organic"/"certified organic" without ever naming a certifying body. No USDA/EU Organic seal found. Original research incorrectly logged this as USDA Certified Organic.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3610,7 +3638,11 @@
           <t>https://tealish.com/en-us/collections/organic-tea</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>N (correction: no certifying body ever named -- not USDA Organic as originally logged)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3643,7 +3675,11 @@
           <t>https://us.threespiritdrinks.com/</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3958,7 +3994,11 @@
           <t>https://racha-organics.com/products/red-mild-sriracha</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3991,7 +4031,11 @@
           <t>https://taimolive.com/</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/global_brand_shortlist.xlsx
+++ b/global_brand_shortlist.xlsx
@@ -1489,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2930,6 +2930,117 @@
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>N (discontinued -- unavailable everywhere checked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>VEGOBEARS</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>USA (Richardson, TX)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Organic vegan gummy bears</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>USDA Certified Organic</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>USDA Organic badge confirmed directly on the brand's own site (vegobears.com); live purchase confirmed at the actual storefront domain, getvegobears.com.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>https://getvegobears.com/products/santa-monica</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Victory Dance Foods</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>USA (Women-owned)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Gluten-free granola</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Certified Gluten-Free (GFCO.org), 1% for the Planet</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Certified Gluten-Free by GFCO.org (named certifying body) plus verified 1% for the Planet member -- brand's own site states "our giving is certified and audited."</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>https://victorydancefoods.com/shop/p/garden-granola-carrot-turmeric-8oz</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ZORA</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>USA (Women-owned) / Ghana-sourced</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Bean-to-bar chocolate</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Gives Back -- quantified, funds one school day per bar</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Every bar sold funds one day of schooling for a girl in rural Ghana through ZORA's own Women's Economic Empowerment Program -- specific and quantified, tied directly to the cocoa-growing region.</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>https://zorachocolate.com/shop/chocolate/pecan-cherry/</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
